--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.64508067152902</v>
+        <v>3.029825609123466</v>
       </c>
       <c r="D2" t="n">
-        <v>17.80814907879337</v>
+        <v>2.893824225303923</v>
       </c>
       <c r="E2" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F2" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.64546025419665</v>
+        <v>7.579887291306956</v>
       </c>
       <c r="D3" t="n">
-        <v>45.96156649085545</v>
+        <v>7.46875455476401</v>
       </c>
       <c r="E3" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F3" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.66089175331926</v>
+        <v>8.88239490991438</v>
       </c>
       <c r="D4" t="n">
-        <v>53.04928221551405</v>
+        <v>8.620508360021034</v>
       </c>
       <c r="E4" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F4" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.61417555865612</v>
+        <v>2.37480352828162</v>
       </c>
       <c r="D5" t="n">
-        <v>13.68814786917019</v>
+        <v>2.224324028740157</v>
       </c>
       <c r="E5" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F5" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>10.12204030393532</v>
+        <v>1.64483154938949</v>
       </c>
       <c r="D6" t="n">
-        <v>10.60510081688792</v>
+        <v>1.723328882744287</v>
       </c>
       <c r="E6" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F6" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.90924154735504</v>
+        <v>5.835251751445195</v>
       </c>
       <c r="D7" t="n">
-        <v>34.1663081615902</v>
+        <v>5.552025076258408</v>
       </c>
       <c r="E7" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F7" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>11.44979696624326</v>
+        <v>1.860592007014529</v>
       </c>
       <c r="D8" t="n">
-        <v>12.30391485599876</v>
+        <v>1.999386164099798</v>
       </c>
       <c r="E8" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F8" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>16.9411269131753</v>
+        <v>2.752933123390986</v>
       </c>
       <c r="D9" t="n">
-        <v>17.11976314500011</v>
+        <v>2.781961511062518</v>
       </c>
       <c r="E9" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F9" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.50147176120623</v>
+        <v>5.606489161196013</v>
       </c>
       <c r="D10" t="n">
-        <v>33.42299136256351</v>
+        <v>5.43123609641657</v>
       </c>
       <c r="E10" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F10" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>22.79733766375557</v>
+        <v>3.70456737036028</v>
       </c>
       <c r="D11" t="n">
-        <v>16.7594284761269</v>
+        <v>2.723407127370621</v>
       </c>
       <c r="E11" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F11" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.87611505006216</v>
+        <v>3.554868695635101</v>
       </c>
       <c r="D12" t="n">
-        <v>20.49365841362189</v>
+        <v>3.330219492213558</v>
       </c>
       <c r="E12" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F12" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>30.7337008402265</v>
+        <v>4.994226386536806</v>
       </c>
       <c r="D13" t="n">
-        <v>17.78136883443088</v>
+        <v>2.889472435595018</v>
       </c>
       <c r="E13" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F13" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>28.20342053453351</v>
+        <v>4.583055836861695</v>
       </c>
       <c r="D14" t="n">
-        <v>27.33747688341945</v>
+        <v>4.442339993555661</v>
       </c>
       <c r="E14" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F14" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>8.829771564454461</v>
+        <v>1.43483787922385</v>
       </c>
       <c r="D15" t="n">
-        <v>30.19709872684825</v>
+        <v>4.90702854311284</v>
       </c>
       <c r="E15" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F15" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>30.50893808083274</v>
+        <v>4.95770243813532</v>
       </c>
       <c r="D16" t="n">
-        <v>23.26821792623987</v>
+        <v>3.781085413013979</v>
       </c>
       <c r="E16" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F16" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>23.80921683305552</v>
+        <v>3.868997735371522</v>
       </c>
       <c r="D17" t="n">
-        <v>23.80149189736555</v>
+        <v>3.867742433321903</v>
       </c>
       <c r="E17" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F17" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>22.21873855539304</v>
+        <v>3.610545015251369</v>
       </c>
       <c r="D18" t="n">
-        <v>23.5888463646235</v>
+        <v>3.833187534251319</v>
       </c>
       <c r="E18" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F18" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>36.84277863422152</v>
+        <v>5.986951528060997</v>
       </c>
       <c r="D19" t="n">
-        <v>30.80861852931458</v>
+        <v>5.00640051101362</v>
       </c>
       <c r="E19" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F19" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>31.89712576785222</v>
+        <v>5.183282937275985</v>
       </c>
       <c r="D20" t="n">
-        <v>29.60922260722365</v>
+        <v>4.811498673673842</v>
       </c>
       <c r="E20" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F20" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>27.89064035857179</v>
+        <v>4.532229058267916</v>
       </c>
       <c r="D21" t="n">
-        <v>28.85970937675756</v>
+        <v>4.689702773723105</v>
       </c>
       <c r="E21" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F21" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>18.62171171205837</v>
+        <v>3.026028153209485</v>
       </c>
       <c r="D22" t="n">
-        <v>18.41556871692017</v>
+        <v>2.992529916499527</v>
       </c>
       <c r="E22" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F22" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>37.6911102575062</v>
+        <v>6.124805416844758</v>
       </c>
       <c r="D23" t="n">
-        <v>39.4618960680449</v>
+        <v>6.412558111057296</v>
       </c>
       <c r="E23" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F23" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>16.64199383562942</v>
+        <v>2.704323998289781</v>
       </c>
       <c r="D24" t="n">
-        <v>16.21033926520656</v>
+        <v>2.634180130596066</v>
       </c>
       <c r="E24" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F24" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>11.51741576471465</v>
+        <v>1.87158006176613</v>
       </c>
       <c r="D25" t="n">
-        <v>11.15169552583282</v>
+        <v>1.812150522947833</v>
       </c>
       <c r="E25" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F25" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>47.15778807655839</v>
+        <v>7.663140562440739</v>
       </c>
       <c r="D26" t="n">
-        <v>46.7258085489941</v>
+        <v>7.592943889211542</v>
       </c>
       <c r="E26" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F26" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>12.54739978637152</v>
+        <v>2.038952465285372</v>
       </c>
       <c r="D27" t="n">
-        <v>12.99192067315631</v>
+        <v>2.1111871093879</v>
       </c>
       <c r="E27" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F27" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>36.56699993186731</v>
+        <v>5.942137488928438</v>
       </c>
       <c r="D28" t="n">
-        <v>36.180303842759</v>
+        <v>5.879299374448337</v>
       </c>
       <c r="E28" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F28" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>29.0989505456958</v>
+        <v>4.728579463675568</v>
       </c>
       <c r="D29" t="n">
-        <v>28.82002724995985</v>
+        <v>4.683254428118476</v>
       </c>
       <c r="E29" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F29" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>21.19289852877299</v>
+        <v>3.443846010925611</v>
       </c>
       <c r="D30" t="n">
-        <v>21.34158578789927</v>
+        <v>3.468007690533632</v>
       </c>
       <c r="E30" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F30" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>26.69149054104427</v>
+        <v>4.337367212919694</v>
       </c>
       <c r="D31" t="n">
-        <v>26.53203002762116</v>
+        <v>4.31145487948844</v>
       </c>
       <c r="E31" t="n">
-        <v>11.47869395933228</v>
+        <v>1.865287768391495</v>
       </c>
       <c r="F31" t="n">
-        <v>10.83529290320228</v>
+        <v>1.76073509677037</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
